--- a/data/trans_orig/P6606-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P6606-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la exposición a manipular cargas pesadas en su trabajo en 2007</t>
+          <t>Población según la exposición a manipular cargas pesadas en su trabajo en 2007 (tasa de respuesta: 99,4%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>122980</t>
+          <t>122795</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>159540</t>
+          <t>158757</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>32,63%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>42,39%</t>
+          <t>42,18%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>81698</t>
+          <t>82363</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>105789</t>
+          <t>107229</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>54,31%</t>
+          <t>54,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>70,32%</t>
+          <t>71,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>213926</t>
+          <t>210304</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>259892</t>
+          <t>258951</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>40,61%</t>
+          <t>39,92%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>49,33%</t>
+          <t>49,16%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>69282</t>
+          <t>68654</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>101960</t>
+          <t>100941</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>26,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>32057</t>
+          <t>32195</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>55216</t>
+          <t>55503</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>36,71%</t>
+          <t>36,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>106425</t>
+          <t>107805</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>150287</t>
+          <t>149258</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>28,33%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>99001</t>
+          <t>99754</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>135842</t>
+          <t>136009</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>36,09%</t>
+          <t>36,14%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4696</t>
+          <t>4618</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>16838</t>
+          <t>15918</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>105260</t>
+          <t>106867</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>146313</t>
+          <t>147020</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>27,91%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23497</t>
+          <t>23984</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>47082</t>
+          <t>45956</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1008</t>
+          <t>1010</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8786</t>
+          <t>8853</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>26240</t>
+          <t>26383</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>50007</t>
+          <t>50580</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,6%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>430845</t>
+          <t>433004</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>495623</t>
+          <t>500610</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>38,37%</t>
+          <t>38,56%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>44,14%</t>
+          <t>44,59%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>436055</t>
+          <t>438657</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>478355</t>
+          <t>477999</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>74,84%</t>
+          <t>75,29%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>82,1%</t>
+          <t>82,04%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>884215</t>
+          <t>883616</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>965408</t>
+          <t>966589</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>51,85%</t>
+          <t>51,81%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>56,61%</t>
+          <t>56,68%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>273594</t>
+          <t>272364</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>335143</t>
+          <t>334186</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>29,76%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>70809</t>
+          <t>72303</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>108367</t>
+          <t>106189</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>358049</t>
+          <t>359771</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>429158</t>
+          <t>429024</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>241298</t>
+          <t>239252</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>300754</t>
+          <t>295533</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>15044</t>
+          <t>15299</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>34162</t>
+          <t>33524</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>259295</t>
+          <t>259422</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>322119</t>
+          <t>320139</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>18,77%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>67012</t>
+          <t>68253</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>104046</t>
+          <t>103004</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6756</t>
+          <t>6302</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>20262</t>
+          <t>20651</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>80581</t>
+          <t>79415</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>120271</t>
+          <t>118833</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,97%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>312970</t>
+          <t>313275</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>346258</t>
+          <t>345806</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,22%</t>
+          <t>77,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,43%</t>
+          <t>85,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>233713</t>
+          <t>233640</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>258822</t>
+          <t>259015</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,08%</t>
+          <t>81,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>89,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>554609</t>
+          <t>554200</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>596830</t>
+          <t>597272</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,97%</t>
+          <t>79,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,05%</t>
+          <t>86,12%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>33679</t>
+          <t>33770</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>60420</t>
+          <t>59697</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>19613</t>
+          <t>19800</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>40006</t>
+          <t>41171</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>58589</t>
+          <t>58207</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>92742</t>
+          <t>91968</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,26%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15165</t>
+          <t>15794</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>35719</t>
+          <t>36216</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2996</t>
+          <t>2702</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14376</t>
+          <t>14813</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>20264</t>
+          <t>20127</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>43359</t>
+          <t>42027</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,06%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2678</t>
+          <t>2466</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14065</t>
+          <t>14368</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>1989</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12238</t>
+          <t>12769</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6470</t>
+          <t>5902</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>21230</t>
+          <t>20861</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>892735</t>
+          <t>891835</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>981429</t>
+          <t>981251</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>46,87%</t>
+          <t>46,83%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>51,53%</t>
+          <t>51,52%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>777593</t>
+          <t>777345</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>828281</t>
+          <t>828077</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>76,13%</t>
+          <t>76,11%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>81,1%</t>
+          <t>81,08%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1683779</t>
+          <t>1681723</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1793542</t>
+          <t>1790728</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>57,55%</t>
+          <t>57,48%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>61,3%</t>
+          <t>61,2%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>396139</t>
+          <t>397426</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>470982</t>
+          <t>471526</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>136042</t>
+          <t>137338</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>181921</t>
+          <t>184283</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>553946</t>
+          <t>549811</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>640151</t>
+          <t>637379</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>21,78%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>372299</t>
+          <t>374603</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>447194</t>
+          <t>447681</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>27675</t>
+          <t>28434</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>52320</t>
+          <t>54215</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>407094</t>
+          <t>407587</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>486085</t>
+          <t>489249</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,72%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>105654</t>
+          <t>107978</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>150380</t>
+          <t>150960</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>13453</t>
+          <t>13415</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>32079</t>
+          <t>32926</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>124624</t>
+          <t>125507</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>172188</t>
+          <t>175001</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,98%</t>
         </is>
       </c>
     </row>
@@ -3045,7 +3045,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la exposición a manipular cargas pesadas en su trabajo en 2012</t>
+          <t>Población según la exposición a manipular cargas pesadas en su trabajo en 2012 (tasa de respuesta: 99,14%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3240,12 +3240,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>23474</t>
+          <t>23148</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>43649</t>
+          <t>44456</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3255,12 +3255,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3275,12 +3275,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>46573</t>
+          <t>46034</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>69156</t>
+          <t>70078</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3290,12 +3290,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>32,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>49,41%</t>
+          <t>50,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3310,12 +3310,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>73445</t>
+          <t>72314</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>106773</t>
+          <t>104304</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3325,12 +3325,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>32,19%</t>
         </is>
       </c>
     </row>
@@ -3353,12 +3353,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>43079</t>
+          <t>43588</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>67376</t>
+          <t>68541</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3368,12 +3368,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>36,61%</t>
+          <t>37,25%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3388,12 +3388,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>48926</t>
+          <t>47533</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>72514</t>
+          <t>72157</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>33,96%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>51,8%</t>
+          <t>51,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3423,12 +3423,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>98234</t>
+          <t>97360</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>132981</t>
+          <t>131662</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>30,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>41,04%</t>
+          <t>40,64%</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>46253</t>
+          <t>46225</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>72699</t>
+          <t>71723</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>39,51%</t>
+          <t>38,98%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6162</t>
+          <t>6141</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>19503</t>
+          <t>19871</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>55842</t>
+          <t>57043</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>85644</t>
+          <t>87042</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>26,87%</t>
         </is>
       </c>
     </row>
@@ -3579,12 +3579,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>27279</t>
+          <t>27781</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>49262</t>
+          <t>50277</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5661</t>
+          <t>6039</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19721</t>
+          <t>19511</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3649,12 +3649,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>36062</t>
+          <t>37088</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>62168</t>
+          <t>63579</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>19,62%</t>
         </is>
       </c>
     </row>
@@ -3809,12 +3809,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>240324</t>
+          <t>242550</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>299655</t>
+          <t>299893</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3824,12 +3824,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>32,98%</t>
+          <t>33,01%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3844,12 +3844,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>245235</t>
+          <t>245178</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>294733</t>
+          <t>292858</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>42,89%</t>
+          <t>42,88%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>51,55%</t>
+          <t>51,22%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3879,12 +3879,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>500620</t>
+          <t>502915</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>580284</t>
+          <t>575405</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>33,97%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>39,2%</t>
+          <t>38,87%</t>
         </is>
       </c>
     </row>
@@ -3922,12 +3922,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>259564</t>
+          <t>257730</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>317220</t>
+          <t>315506</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3957,12 +3957,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>161018</t>
+          <t>158974</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>207805</t>
+          <t>206850</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,34%</t>
+          <t>36,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>433194</t>
+          <t>434594</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>508487</t>
+          <t>504372</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4007,12 +4007,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>29,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>34,07%</t>
         </is>
       </c>
     </row>
@@ -4035,12 +4035,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>198800</t>
+          <t>202234</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>253246</t>
+          <t>254063</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>27,96%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>69872</t>
+          <t>69810</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>106140</t>
+          <t>106187</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>280413</t>
+          <t>284722</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>344034</t>
+          <t>348358</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>23,53%</t>
         </is>
       </c>
     </row>
@@ -4148,12 +4148,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>103324</t>
+          <t>103624</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>145611</t>
+          <t>146996</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>22168</t>
+          <t>21829</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>45439</t>
+          <t>44884</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>133260</t>
+          <t>132869</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>182238</t>
+          <t>182644</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,34%</t>
         </is>
       </c>
     </row>
@@ -4378,12 +4378,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>187836</t>
+          <t>188143</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>223665</t>
+          <t>225056</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4393,12 +4393,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>59,39%</t>
+          <t>59,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>70,72%</t>
+          <t>71,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>170099</t>
+          <t>172812</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>197992</t>
+          <t>198327</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4428,12 +4428,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,41%</t>
+          <t>73,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,29%</t>
+          <t>84,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>366920</t>
+          <t>368515</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>412861</t>
+          <t>416484</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4463,12 +4463,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,57%</t>
+          <t>66,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>74,91%</t>
+          <t>75,57%</t>
         </is>
       </c>
     </row>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>97172</t>
+          <t>98138</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>31,03%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>26262</t>
+          <t>25960</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>51078</t>
+          <t>49337</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4541,12 +4541,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>98222</t>
+          <t>98997</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>138542</t>
+          <t>139759</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4576,12 +4576,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>25,36%</t>
         </is>
       </c>
     </row>
@@ -4604,12 +4604,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18079</t>
+          <t>17725</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>40474</t>
+          <t>41630</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2837</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14746</t>
+          <t>15404</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4654,12 +4654,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>24076</t>
+          <t>23131</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>50913</t>
+          <t>47737</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4689,12 +4689,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>8,66%</t>
         </is>
       </c>
     </row>
@@ -4717,12 +4717,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>943</t>
+          <t>939</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9002</t>
+          <t>9462</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4737,7 +4737,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>974</t>
+          <t>965</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11908</t>
+          <t>11024</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4787,12 +4787,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3065</t>
+          <t>2917</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>16357</t>
+          <t>16020</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4802,12 +4802,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,91%</t>
         </is>
       </c>
     </row>
@@ -4947,12 +4947,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>473009</t>
+          <t>475627</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>550420</t>
+          <t>549807</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4962,12 +4962,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>33,76%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>39,07%</t>
+          <t>39,02%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>482440</t>
+          <t>479369</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>541635</t>
+          <t>543670</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4997,12 +4997,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>50,96%</t>
+          <t>50,64%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>57,22%</t>
+          <t>57,43%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>971682</t>
+          <t>972942</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1070603</t>
+          <t>1079741</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5032,12 +5032,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>41,25%</t>
+          <t>41,3%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>45,45%</t>
+          <t>45,84%</t>
         </is>
       </c>
     </row>
@@ -5060,12 +5060,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>386840</t>
+          <t>388187</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>455253</t>
+          <t>460550</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5075,12 +5075,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>32,31%</t>
+          <t>32,69%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>253131</t>
+          <t>251884</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>306780</t>
+          <t>309284</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5110,12 +5110,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>32,41%</t>
+          <t>32,67%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>660271</t>
+          <t>654550</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>752037</t>
+          <t>753407</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>31,98%</t>
         </is>
       </c>
     </row>
@@ -5173,12 +5173,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>281114</t>
+          <t>282042</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>344063</t>
+          <t>344691</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5208,12 +5208,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>87687</t>
+          <t>86774</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>126071</t>
+          <t>126294</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5223,12 +5223,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>383098</t>
+          <t>382480</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>455724</t>
+          <t>459229</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5258,12 +5258,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,5%</t>
         </is>
       </c>
     </row>
@@ -5286,12 +5286,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>142126</t>
+          <t>141503</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>188677</t>
+          <t>190865</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5301,12 +5301,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5321,12 +5321,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>34779</t>
+          <t>33667</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>62868</t>
+          <t>62879</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5336,7 +5336,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -5356,12 +5356,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>184388</t>
+          <t>183763</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>242399</t>
+          <t>241587</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5371,12 +5371,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,26%</t>
         </is>
       </c>
     </row>
@@ -5552,7 +5552,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la exposición a manipular cargas pesadas en su trabajo en 2016</t>
+          <t>Población según la exposición a manipular cargas pesadas en su trabajo en 2016 (tasa de respuesta: 99,4%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5747,12 +5747,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10991</t>
+          <t>11065</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27774</t>
+          <t>27899</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5762,12 +5762,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5782,12 +5782,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15039</t>
+          <t>14797</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>30451</t>
+          <t>30526</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5797,12 +5797,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>42,24%</t>
+          <t>42,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5817,12 +5817,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>30007</t>
+          <t>30177</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>52565</t>
+          <t>53396</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5832,12 +5832,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>25,51%</t>
         </is>
       </c>
     </row>
@@ -5860,12 +5860,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>26989</t>
+          <t>27435</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>48504</t>
+          <t>48401</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5875,12 +5875,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>35,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5895,12 +5895,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17181</t>
+          <t>17518</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>32728</t>
+          <t>32735</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5910,12 +5910,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>45,4%</t>
+          <t>45,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5930,12 +5930,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>50164</t>
+          <t>49287</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>76358</t>
+          <t>75814</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5945,12 +5945,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,48%</t>
+          <t>36,22%</t>
         </is>
       </c>
     </row>
@@ -5973,12 +5973,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>34207</t>
+          <t>34677</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>57476</t>
+          <t>55737</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>41,88%</t>
+          <t>40,61%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6008,12 +6008,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>9680</t>
+          <t>9753</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>24226</t>
+          <t>24003</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6023,12 +6023,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>33,61%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>48151</t>
+          <t>48030</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>74707</t>
+          <t>74178</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6058,12 +6058,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>35,69%</t>
+          <t>35,44%</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>26268</t>
+          <t>26427</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>48620</t>
+          <t>47907</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,43%</t>
+          <t>34,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4595</t>
+          <t>4829</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16155</t>
+          <t>15817</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>34677</t>
+          <t>34874</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>59018</t>
+          <t>60299</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>28,81%</t>
         </is>
       </c>
     </row>
@@ -6316,12 +6316,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>272575</t>
+          <t>270381</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>331017</t>
+          <t>331652</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6331,12 +6331,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>29,43%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>36,03%</t>
+          <t>36,1%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6351,12 +6351,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>286363</t>
+          <t>285517</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>335999</t>
+          <t>336926</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6366,12 +6366,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>43,94%</t>
+          <t>43,81%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>51,55%</t>
+          <t>51,69%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6386,12 +6386,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>571048</t>
+          <t>572974</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>651717</t>
+          <t>649955</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>36,36%</t>
+          <t>36,49%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>41,5%</t>
+          <t>41,39%</t>
         </is>
       </c>
     </row>
@@ -6429,12 +6429,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>263129</t>
+          <t>261038</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>317987</t>
+          <t>319441</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6444,12 +6444,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>34,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>182063</t>
+          <t>177388</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>230355</t>
+          <t>226418</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>27,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>34,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6499,12 +6499,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>458803</t>
+          <t>454744</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>531354</t>
+          <t>531270</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6514,12 +6514,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>33,83%</t>
         </is>
       </c>
     </row>
@@ -6542,12 +6542,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>187100</t>
+          <t>189472</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>238171</t>
+          <t>243044</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6557,12 +6557,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>80177</t>
+          <t>80201</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>116419</t>
+          <t>116019</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6597,7 +6597,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6612,12 +6612,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>281432</t>
+          <t>280144</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>342516</t>
+          <t>345187</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6627,12 +6627,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>21,98%</t>
         </is>
       </c>
     </row>
@@ -6655,12 +6655,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>96252</t>
+          <t>93710</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>137390</t>
+          <t>135220</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6670,12 +6670,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6690,12 +6690,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>28122</t>
+          <t>28002</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>52549</t>
+          <t>52801</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6705,12 +6705,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6725,12 +6725,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>128703</t>
+          <t>128527</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>178167</t>
+          <t>176460</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6740,12 +6740,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,24%</t>
         </is>
       </c>
     </row>
@@ -6885,12 +6885,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>227086</t>
+          <t>226714</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>260669</t>
+          <t>261918</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6900,12 +6900,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>65,14%</t>
+          <t>65,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>74,78%</t>
+          <t>75,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6920,12 +6920,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>211440</t>
+          <t>210020</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>241624</t>
+          <t>242072</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6935,12 +6935,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,55%</t>
+          <t>68,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>78,33%</t>
+          <t>78,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6955,12 +6955,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>448803</t>
+          <t>450263</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>493859</t>
+          <t>498947</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6970,12 +6970,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>68,31%</t>
+          <t>68,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,16%</t>
+          <t>75,94%</t>
         </is>
       </c>
     </row>
@@ -6998,12 +6998,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>52249</t>
+          <t>52013</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>82622</t>
+          <t>81615</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7013,12 +7013,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7033,12 +7033,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>36808</t>
+          <t>38540</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>62979</t>
+          <t>64279</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7048,12 +7048,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -7068,12 +7068,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>95937</t>
+          <t>95215</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>135017</t>
+          <t>135604</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7083,12 +7083,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,64%</t>
         </is>
       </c>
     </row>
@@ -7111,12 +7111,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>20606</t>
+          <t>20305</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>42890</t>
+          <t>41354</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7126,12 +7126,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7146,12 +7146,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12452</t>
+          <t>12131</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>30448</t>
+          <t>29906</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7161,12 +7161,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7181,12 +7181,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>36697</t>
+          <t>37080</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>64783</t>
+          <t>64020</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7196,12 +7196,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,74%</t>
         </is>
       </c>
     </row>
@@ -7224,12 +7224,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3863</t>
+          <t>3778</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16495</t>
+          <t>16473</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7239,7 +7239,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -7259,12 +7259,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6683</t>
+          <t>6003</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>20117</t>
+          <t>19455</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7274,12 +7274,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7294,12 +7294,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>13594</t>
+          <t>13169</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>30290</t>
+          <t>31394</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7309,12 +7309,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,78%</t>
         </is>
       </c>
     </row>
@@ -7454,12 +7454,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>528252</t>
+          <t>527813</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>601662</t>
+          <t>599838</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7469,12 +7469,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>37,61%</t>
+          <t>37,58%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>42,84%</t>
+          <t>42,71%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7489,12 +7489,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>531195</t>
+          <t>530026</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>594573</t>
+          <t>593148</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7504,12 +7504,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>51,46%</t>
+          <t>51,34%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>57,6%</t>
+          <t>57,46%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7524,12 +7524,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1078999</t>
+          <t>1076833</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1170322</t>
+          <t>1181149</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7539,12 +7539,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>44,28%</t>
+          <t>44,19%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>48,03%</t>
+          <t>48,47%</t>
         </is>
       </c>
     </row>
@@ -7567,12 +7567,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>361327</t>
+          <t>358274</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>429578</t>
+          <t>424951</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7582,12 +7582,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7602,12 +7602,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>249233</t>
+          <t>251137</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>306904</t>
+          <t>305452</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7617,12 +7617,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>29,59%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7637,12 +7637,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>627143</t>
+          <t>627275</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>713514</t>
+          <t>714233</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7657,7 +7657,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>29,31%</t>
         </is>
       </c>
     </row>
@@ -7680,12 +7680,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>257628</t>
+          <t>257171</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>318120</t>
+          <t>318386</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7695,12 +7695,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7715,12 +7715,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>112999</t>
+          <t>114207</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>155086</t>
+          <t>155819</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7730,12 +7730,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7750,12 +7750,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>385740</t>
+          <t>384730</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>458365</t>
+          <t>460270</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7765,12 +7765,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,89%</t>
         </is>
       </c>
     </row>
@@ -7793,12 +7793,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>133549</t>
+          <t>134133</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>183949</t>
+          <t>183090</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7808,12 +7808,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7828,12 +7828,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>47380</t>
+          <t>46941</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>76563</t>
+          <t>77315</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7863,12 +7863,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>190701</t>
+          <t>192819</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>251287</t>
+          <t>246530</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,12%</t>
         </is>
       </c>
     </row>
@@ -8059,7 +8059,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la exposición a manipular cargas pesadas en su trabajo en 2023</t>
+          <t>Población según la exposición a manipular cargas pesadas en su trabajo en 2023 (tasa de respuesta: 99,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11168</t>
+          <t>10305</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25883</t>
+          <t>26475</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8269,12 +8269,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>39,57%</t>
+          <t>40,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8289,12 +8289,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5541</t>
+          <t>5419</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14104</t>
+          <t>14472</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>36,05%</t>
+          <t>36,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8324,12 +8324,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18703</t>
+          <t>18976</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>36522</t>
+          <t>36897</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8339,12 +8339,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>34,94%</t>
+          <t>35,3%</t>
         </is>
       </c>
     </row>
@@ -8367,12 +8367,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8652</t>
+          <t>8955</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22858</t>
+          <t>23308</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8382,12 +8382,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34,94%</t>
+          <t>35,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8402,12 +8402,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11827</t>
+          <t>11849</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21188</t>
+          <t>21629</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8417,12 +8417,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,23%</t>
+          <t>30,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>54,16%</t>
+          <t>55,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8437,12 +8437,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>23440</t>
+          <t>22473</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>40270</t>
+          <t>40324</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8452,12 +8452,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>38,52%</t>
+          <t>38,57%</t>
         </is>
       </c>
     </row>
@@ -8480,12 +8480,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11077</t>
+          <t>11296</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>26675</t>
+          <t>27457</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8495,47 +8495,47 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
+          <t>17,27%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>41,97%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>10594</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>6625</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>16215</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>27,08%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
           <t>16,93%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>40,78%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>10594</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>6066</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>16111</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>27,08%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>15,5%</t>
-        </is>
-      </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>41,18%</t>
+          <t>41,45%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8550,12 +8550,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>20687</t>
+          <t>20161</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>38417</t>
+          <t>38189</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8565,12 +8565,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>36,53%</t>
         </is>
       </c>
     </row>
@@ -8593,12 +8593,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9630</t>
+          <t>9879</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23288</t>
+          <t>24277</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8608,12 +8608,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,6%</t>
+          <t>37,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8628,12 +8628,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>943</t>
+          <t>856</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6073</t>
+          <t>6474</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8663,12 +8663,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11776</t>
+          <t>11988</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>26688</t>
+          <t>27060</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8678,12 +8678,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,89%</t>
         </is>
       </c>
     </row>
@@ -8823,12 +8823,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>218781</t>
+          <t>213893</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>634521</t>
+          <t>629958</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8838,12 +8838,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>78,79%</t>
+          <t>78,22%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8858,12 +8858,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>127018</t>
+          <t>126420</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>189828</t>
+          <t>189033</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8873,12 +8873,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>42,97%</t>
+          <t>42,79%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8893,12 +8893,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>389079</t>
+          <t>389197</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>861049</t>
+          <t>901570</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8908,12 +8908,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>31,21%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>69,04%</t>
+          <t>72,29%</t>
         </is>
       </c>
     </row>
@@ -8936,12 +8936,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>75102</t>
+          <t>76994</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>253945</t>
+          <t>257607</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8951,12 +8951,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>31,53%</t>
+          <t>31,99%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8971,12 +8971,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>140447</t>
+          <t>141401</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>233577</t>
+          <t>232727</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8986,12 +8986,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>31,79%</t>
+          <t>32,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>52,87%</t>
+          <t>52,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9006,12 +9006,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>182709</t>
+          <t>178053</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>448191</t>
+          <t>450538</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9021,12 +9021,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,94%</t>
+          <t>36,13%</t>
         </is>
       </c>
     </row>
@@ -9049,12 +9049,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>65100</t>
+          <t>62957</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>230245</t>
+          <t>229872</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9064,12 +9064,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9084,12 +9084,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>48270</t>
+          <t>49414</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>78684</t>
+          <t>80522</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9099,12 +9099,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9119,12 +9119,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>122234</t>
+          <t>107634</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>281714</t>
+          <t>283764</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9134,12 +9134,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,75%</t>
         </is>
       </c>
     </row>
@@ -9162,12 +9162,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>31471</t>
+          <t>30334</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>122582</t>
+          <t>121863</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9197,12 +9197,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>29638</t>
+          <t>28685</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>54999</t>
+          <t>54128</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9212,12 +9212,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9232,12 +9232,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>65108</t>
+          <t>60830</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>160610</t>
+          <t>160596</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9247,7 +9247,7 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -9392,12 +9392,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>175369</t>
+          <t>174337</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>203079</t>
+          <t>203460</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9407,12 +9407,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,45%</t>
+          <t>72,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,9%</t>
+          <t>84,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9427,12 +9427,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>144732</t>
+          <t>145078</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>165294</t>
+          <t>165049</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9442,12 +9442,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,71%</t>
+          <t>72,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,03%</t>
+          <t>82,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9462,12 +9462,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>329708</t>
+          <t>327884</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>362750</t>
+          <t>362285</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9477,12 +9477,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,74%</t>
+          <t>74,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,23%</t>
+          <t>82,13%</t>
         </is>
       </c>
     </row>
@@ -9505,12 +9505,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>24480</t>
+          <t>24637</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>47966</t>
+          <t>48964</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9520,12 +9520,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -9540,12 +9540,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>22003</t>
+          <t>22106</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>40463</t>
+          <t>39772</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9555,12 +9555,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -9575,12 +9575,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>51722</t>
+          <t>52216</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>79748</t>
+          <t>82214</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -9590,12 +9590,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,64%</t>
         </is>
       </c>
     </row>
@@ -9618,12 +9618,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5542</t>
+          <t>5324</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19392</t>
+          <t>18373</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9633,12 +9633,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9653,12 +9653,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3247</t>
+          <t>3220</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11095</t>
+          <t>11570</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9668,12 +9668,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9688,12 +9688,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11094</t>
+          <t>11581</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>26599</t>
+          <t>26538</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9703,12 +9703,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,02%</t>
         </is>
       </c>
     </row>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>509</t>
+          <t>168</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17108</t>
+          <t>17649</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9746,12 +9746,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9766,12 +9766,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3301</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12940</t>
+          <t>13250</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9781,12 +9781,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9801,12 +9801,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5651</t>
+          <t>5110</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>23963</t>
+          <t>22938</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9816,12 +9816,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,2%</t>
         </is>
       </c>
     </row>
@@ -9961,12 +9961,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>459185</t>
+          <t>458111</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>849522</t>
+          <t>831639</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9976,12 +9976,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>41,17%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>76,34%</t>
+          <t>74,73%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9996,12 +9996,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>284370</t>
+          <t>271170</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>361670</t>
+          <t>360247</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10011,12 +10011,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>41,82%</t>
+          <t>39,88%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>53,19%</t>
+          <t>52,98%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10031,12 +10031,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>789952</t>
+          <t>787313</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1236507</t>
+          <t>1240708</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10046,12 +10046,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>44,06%</t>
+          <t>43,92%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>68,97%</t>
+          <t>69,21%</t>
         </is>
       </c>
     </row>
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>118007</t>
+          <t>124808</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>296114</t>
+          <t>292637</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10089,12 +10089,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10109,12 +10109,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>183779</t>
+          <t>183920</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>296393</t>
+          <t>305646</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10124,12 +10124,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>27,05%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>43,59%</t>
+          <t>44,95%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10144,12 +10144,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>280688</t>
+          <t>280873</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>536661</t>
+          <t>527908</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10159,12 +10159,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>29,45%</t>
         </is>
       </c>
     </row>
@@ -10187,12 +10187,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>94654</t>
+          <t>92489</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>242681</t>
+          <t>245096</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10202,12 +10202,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10222,12 +10222,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>66103</t>
+          <t>65527</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>98516</t>
+          <t>99650</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10237,12 +10237,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10257,12 +10257,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>171191</t>
+          <t>172609</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>317736</t>
+          <t>322327</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,98%</t>
         </is>
       </c>
     </row>
@@ -10300,12 +10300,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>50982</t>
+          <t>56064</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>135078</t>
+          <t>135200</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10315,12 +10315,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10335,12 +10335,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>37745</t>
+          <t>37367</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>64530</t>
+          <t>63958</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10350,12 +10350,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10370,12 +10370,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>95916</t>
+          <t>96146</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>182693</t>
+          <t>186440</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10385,12 +10385,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,4%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P6606-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P6606-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>122795</t>
+          <t>120950</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>158757</t>
+          <t>159291</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>32,14%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>42,18%</t>
+          <t>42,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>82363</t>
+          <t>82667</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>107229</t>
+          <t>106138</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>54,75%</t>
+          <t>54,95%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>71,28%</t>
+          <t>70,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>210304</t>
+          <t>213921</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>258951</t>
+          <t>258691</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>39,92%</t>
+          <t>40,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>49,16%</t>
+          <t>49,11%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>68654</t>
+          <t>70240</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>100941</t>
+          <t>103418</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>27,48%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>32195</t>
+          <t>32097</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>55503</t>
+          <t>54204</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>36,9%</t>
+          <t>36,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>107805</t>
+          <t>108590</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>149258</t>
+          <t>147917</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>28,08%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>99754</t>
+          <t>97531</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>136009</t>
+          <t>136700</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>25,91%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>36,14%</t>
+          <t>36,32%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4618</t>
+          <t>4932</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>15918</t>
+          <t>17436</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>106867</t>
+          <t>107362</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>147020</t>
+          <t>146950</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>27,89%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23984</t>
+          <t>23866</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>45956</t>
+          <t>44951</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1010</t>
+          <t>1026</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8853</t>
+          <t>8620</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>26383</t>
+          <t>27144</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>50580</t>
+          <t>51336</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,74%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>433004</t>
+          <t>430786</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>500610</t>
+          <t>500817</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>38,56%</t>
+          <t>38,37%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>44,59%</t>
+          <t>44,6%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>438657</t>
+          <t>437870</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>477999</t>
+          <t>478013</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>75,29%</t>
+          <t>75,15%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>883616</t>
+          <t>884088</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>966589</t>
+          <t>966198</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>51,81%</t>
+          <t>51,84%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>56,68%</t>
+          <t>56,65%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>272364</t>
+          <t>272792</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>334186</t>
+          <t>335964</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>29,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>72303</t>
+          <t>71702</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>106189</t>
+          <t>106518</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>359771</t>
+          <t>355920</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>429024</t>
+          <t>429331</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>25,17%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>239252</t>
+          <t>239720</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>295533</t>
+          <t>294359</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>26,22%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>15299</t>
+          <t>15222</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>33524</t>
+          <t>34323</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>259422</t>
+          <t>257466</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>320139</t>
+          <t>320474</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>18,79%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>68253</t>
+          <t>69692</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>103004</t>
+          <t>104467</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6302</t>
+          <t>6609</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>20651</t>
+          <t>21225</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>79415</t>
+          <t>80742</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>118833</t>
+          <t>121771</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,14%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>313275</t>
+          <t>312189</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>345806</t>
+          <t>344987</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,29%</t>
+          <t>77,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,32%</t>
+          <t>85,12%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>233640</t>
+          <t>234699</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>259015</t>
+          <t>258444</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,05%</t>
+          <t>81,42%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,86%</t>
+          <t>89,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>554200</t>
+          <t>554408</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>597272</t>
+          <t>595721</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,91%</t>
+          <t>79,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,12%</t>
+          <t>85,89%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>33770</t>
+          <t>34295</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>59697</t>
+          <t>59459</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>19800</t>
+          <t>19329</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>41171</t>
+          <t>39458</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>58207</t>
+          <t>58874</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>91968</t>
+          <t>92862</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,39%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15794</t>
+          <t>15000</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>36216</t>
+          <t>36239</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,7 +2112,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2702</t>
+          <t>2763</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14813</t>
+          <t>14624</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>20127</t>
+          <t>20479</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>42027</t>
+          <t>43712</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,3%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2466</t>
+          <t>2651</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14368</t>
+          <t>15027</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1989</t>
+          <t>1980</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12769</t>
+          <t>11923</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5902</t>
+          <t>6370</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>20861</t>
+          <t>21010</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,03%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>891835</t>
+          <t>890264</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>981251</t>
+          <t>978190</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>46,83%</t>
+          <t>46,75%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>51,52%</t>
+          <t>51,36%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>777345</t>
+          <t>773445</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>828077</t>
+          <t>827451</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>76,11%</t>
+          <t>75,73%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>81,08%</t>
+          <t>81,02%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1681723</t>
+          <t>1681910</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1790728</t>
+          <t>1785751</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>61,2%</t>
+          <t>61,03%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>397426</t>
+          <t>397864</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>471526</t>
+          <t>474167</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>137338</t>
+          <t>136324</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>184283</t>
+          <t>184846</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>549811</t>
+          <t>551003</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>637379</t>
+          <t>639072</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,84%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>374603</t>
+          <t>374678</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>447681</t>
+          <t>448317</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2686,7 +2686,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>28434</t>
+          <t>28532</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>54215</t>
+          <t>53796</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>407587</t>
+          <t>406247</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>489249</t>
+          <t>487717</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,67%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>107978</t>
+          <t>106054</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>150960</t>
+          <t>149857</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>13415</t>
+          <t>13732</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>32926</t>
+          <t>32010</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>125507</t>
+          <t>124847</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>175001</t>
+          <t>172187</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,89%</t>
         </is>
       </c>
     </row>
@@ -3240,12 +3240,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>23148</t>
+          <t>22497</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>44456</t>
+          <t>42441</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3255,12 +3255,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3275,12 +3275,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>46034</t>
+          <t>47327</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>70078</t>
+          <t>69564</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3290,12 +3290,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>33,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>50,06%</t>
+          <t>49,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3310,12 +3310,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>72314</t>
+          <t>75288</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>104304</t>
+          <t>108163</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3325,12 +3325,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>32,19%</t>
+          <t>33,38%</t>
         </is>
       </c>
     </row>
@@ -3353,12 +3353,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>43588</t>
+          <t>43136</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>68541</t>
+          <t>69067</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3368,12 +3368,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>37,25%</t>
+          <t>37,53%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3388,12 +3388,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>47533</t>
+          <t>49806</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>72157</t>
+          <t>72077</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>33,96%</t>
+          <t>35,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>51,55%</t>
+          <t>51,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3423,12 +3423,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>97360</t>
+          <t>97447</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>131662</t>
+          <t>133216</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>30,05%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>40,64%</t>
+          <t>41,12%</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>46225</t>
+          <t>45260</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>71723</t>
+          <t>72254</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>38,98%</t>
+          <t>39,26%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6141</t>
+          <t>5964</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>19871</t>
+          <t>19031</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>57043</t>
+          <t>55758</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>87042</t>
+          <t>85564</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>26,41%</t>
         </is>
       </c>
     </row>
@@ -3579,12 +3579,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>27781</t>
+          <t>27937</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>50277</t>
+          <t>50177</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>27,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6039</t>
+          <t>5283</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19511</t>
+          <t>19734</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3649,12 +3649,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>37088</t>
+          <t>36574</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>63579</t>
+          <t>65134</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>20,1%</t>
         </is>
       </c>
     </row>
@@ -3809,12 +3809,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>242550</t>
+          <t>244064</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>299893</t>
+          <t>303121</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3824,12 +3824,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3844,12 +3844,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>245178</t>
+          <t>243729</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>292858</t>
+          <t>294273</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>42,88%</t>
+          <t>42,63%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>51,22%</t>
+          <t>51,47%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3879,12 +3879,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>502915</t>
+          <t>505635</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>575405</t>
+          <t>579302</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>34,16%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>38,87%</t>
+          <t>39,13%</t>
         </is>
       </c>
     </row>
@@ -3922,12 +3922,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>257730</t>
+          <t>260787</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>315506</t>
+          <t>316782</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,72%</t>
+          <t>34,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3957,12 +3957,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>158974</t>
+          <t>160693</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>206850</t>
+          <t>206489</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,18%</t>
+          <t>36,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>434594</t>
+          <t>438199</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>504372</t>
+          <t>506740</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4007,12 +4007,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>29,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>34,23%</t>
         </is>
       </c>
     </row>
@@ -4035,12 +4035,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>202234</t>
+          <t>200693</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>254063</t>
+          <t>253313</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>69810</t>
+          <t>71308</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>106187</t>
+          <t>107065</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>284722</t>
+          <t>282147</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>348358</t>
+          <t>346524</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,41%</t>
         </is>
       </c>
     </row>
@@ -4148,12 +4148,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>103624</t>
+          <t>104874</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>146996</t>
+          <t>148663</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>21829</t>
+          <t>21196</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>44884</t>
+          <t>44539</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>132869</t>
+          <t>132443</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>182644</t>
+          <t>183225</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,38%</t>
         </is>
       </c>
     </row>
@@ -4378,12 +4378,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>188143</t>
+          <t>187979</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>225056</t>
+          <t>224803</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4393,82 +4393,82 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>59,49%</t>
+          <t>59,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
+          <t>71,08%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>186095</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>170497</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>199050</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>79,22%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>72,58%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>84,74%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>356</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>392218</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>368748</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>412991</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
           <t>71,16%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>186095</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>172812</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>198327</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>79,22%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>73,57%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>84,43%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>356</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>392218</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>368515</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>416484</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>71,16%</t>
-        </is>
-      </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,86%</t>
+          <t>66,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,57%</t>
+          <t>74,93%</t>
         </is>
       </c>
     </row>
@@ -4491,12 +4491,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>63942</t>
+          <t>61785</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>98138</t>
+          <t>95720</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>31,03%</t>
+          <t>30,27%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>25960</t>
+          <t>27092</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>49337</t>
+          <t>51709</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4541,12 +4541,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>98997</t>
+          <t>98648</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>139759</t>
+          <t>137089</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4576,12 +4576,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>24,87%</t>
         </is>
       </c>
     </row>
@@ -4604,12 +4604,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17725</t>
+          <t>16877</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>41630</t>
+          <t>39033</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>2830</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15404</t>
+          <t>15112</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4654,12 +4654,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>23131</t>
+          <t>23404</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>47737</t>
+          <t>48780</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4689,12 +4689,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,85%</t>
         </is>
       </c>
     </row>
@@ -4717,12 +4717,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>939</t>
+          <t>940</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9462</t>
+          <t>9440</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>965</t>
+          <t>972</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11024</t>
+          <t>10954</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4787,12 +4787,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2917</t>
+          <t>2894</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>16020</t>
+          <t>15807</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4807,7 +4807,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,87%</t>
         </is>
       </c>
     </row>
@@ -4947,12 +4947,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>475627</t>
+          <t>473011</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>549807</t>
+          <t>546296</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4962,12 +4962,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>33,57%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>39,02%</t>
+          <t>38,77%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>479369</t>
+          <t>480674</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>543670</t>
+          <t>546826</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4997,12 +4997,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>50,64%</t>
+          <t>50,78%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>57,43%</t>
+          <t>57,76%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>972942</t>
+          <t>970585</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1079741</t>
+          <t>1070783</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5032,12 +5032,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>41,3%</t>
+          <t>41,2%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>45,84%</t>
+          <t>45,46%</t>
         </is>
       </c>
     </row>
@@ -5060,12 +5060,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>388187</t>
+          <t>387043</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>460550</t>
+          <t>458938</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5075,12 +5075,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>32,57%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>251884</t>
+          <t>252618</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>309284</t>
+          <t>310431</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5110,12 +5110,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>654550</t>
+          <t>657036</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>753407</t>
+          <t>750853</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>31,88%</t>
         </is>
       </c>
     </row>
@@ -5173,12 +5173,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>282042</t>
+          <t>281391</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>344691</t>
+          <t>346021</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5208,12 +5208,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>86774</t>
+          <t>87587</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>126294</t>
+          <t>126924</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5223,12 +5223,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>382480</t>
+          <t>381873</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>459229</t>
+          <t>458575</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5258,12 +5258,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,47%</t>
         </is>
       </c>
     </row>
@@ -5286,12 +5286,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>141503</t>
+          <t>141763</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>190865</t>
+          <t>191962</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5301,12 +5301,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5321,12 +5321,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>33667</t>
+          <t>34224</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>62879</t>
+          <t>64753</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5336,12 +5336,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5356,12 +5356,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>183763</t>
+          <t>186014</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>241587</t>
+          <t>243196</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5371,12 +5371,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,32%</t>
         </is>
       </c>
     </row>
@@ -5747,12 +5747,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11065</t>
+          <t>11083</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27899</t>
+          <t>28096</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5762,12 +5762,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5782,12 +5782,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14797</t>
+          <t>15206</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>30526</t>
+          <t>30924</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5797,12 +5797,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>42,35%</t>
+          <t>42,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5817,12 +5817,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>30177</t>
+          <t>28873</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>53396</t>
+          <t>51717</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5832,12 +5832,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>24,71%</t>
         </is>
       </c>
     </row>
@@ -5860,12 +5860,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>27435</t>
+          <t>26938</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>48401</t>
+          <t>48574</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5875,12 +5875,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,27%</t>
+          <t>35,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5895,12 +5895,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17518</t>
+          <t>17415</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>32735</t>
+          <t>33016</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5910,12 +5910,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>45,41%</t>
+          <t>45,8%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5930,12 +5930,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>49287</t>
+          <t>48731</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>75814</t>
+          <t>75589</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5945,12 +5945,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,22%</t>
+          <t>36,11%</t>
         </is>
       </c>
     </row>
@@ -5973,12 +5973,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>34677</t>
+          <t>34798</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>55737</t>
+          <t>56264</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>40,61%</t>
+          <t>41,0%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6008,12 +6008,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>9753</t>
+          <t>9702</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>24003</t>
+          <t>23816</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6023,12 +6023,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>33,04%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>48030</t>
+          <t>48277</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>74178</t>
+          <t>72844</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6058,12 +6058,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>34,8%</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>26427</t>
+          <t>27439</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>47907</t>
+          <t>48767</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>35,53%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4829</t>
+          <t>4860</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15817</t>
+          <t>16405</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>34874</t>
+          <t>34936</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>60299</t>
+          <t>59769</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>28,55%</t>
         </is>
       </c>
     </row>
@@ -6316,12 +6316,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>270381</t>
+          <t>273245</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>331652</t>
+          <t>328052</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6331,12 +6331,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>29,74%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>36,1%</t>
+          <t>35,71%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6351,12 +6351,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>285517</t>
+          <t>285597</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>336926</t>
+          <t>338624</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6366,12 +6366,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>43,81%</t>
+          <t>43,82%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>51,69%</t>
+          <t>51,95%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6386,12 +6386,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>572974</t>
+          <t>577213</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>649955</t>
+          <t>653622</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>36,49%</t>
+          <t>36,76%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>41,39%</t>
+          <t>41,62%</t>
         </is>
       </c>
     </row>
@@ -6429,12 +6429,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>261038</t>
+          <t>262224</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>319441</t>
+          <t>317119</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6444,12 +6444,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,77%</t>
+          <t>34,52%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>177388</t>
+          <t>179325</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>226418</t>
+          <t>225214</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>34,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6499,12 +6499,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>454744</t>
+          <t>460133</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>531270</t>
+          <t>530127</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6514,12 +6514,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>33,76%</t>
         </is>
       </c>
     </row>
@@ -6542,12 +6542,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>189472</t>
+          <t>188315</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>243044</t>
+          <t>240065</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6557,12 +6557,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>80201</t>
+          <t>80115</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>116019</t>
+          <t>117261</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6592,12 +6592,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6612,12 +6612,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>280144</t>
+          <t>278764</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>345187</t>
+          <t>343110</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6627,12 +6627,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>21,85%</t>
         </is>
       </c>
     </row>
@@ -6655,12 +6655,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>93710</t>
+          <t>94949</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>135220</t>
+          <t>135326</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6670,12 +6670,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6690,12 +6690,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>28002</t>
+          <t>27670</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>52801</t>
+          <t>53574</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6705,12 +6705,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6725,12 +6725,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>128527</t>
+          <t>129680</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>176460</t>
+          <t>176479</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6740,7 +6740,7 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>226714</t>
+          <t>226775</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>261918</t>
+          <t>262337</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6900,12 +6900,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>65,04%</t>
+          <t>65,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>75,13%</t>
+          <t>75,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6920,12 +6920,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>210020</t>
+          <t>210748</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>242072</t>
+          <t>241531</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6935,12 +6935,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,09%</t>
+          <t>68,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>78,48%</t>
+          <t>78,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6955,12 +6955,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>450263</t>
+          <t>447835</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>498947</t>
+          <t>495880</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6970,12 +6970,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>68,53%</t>
+          <t>68,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,94%</t>
+          <t>75,47%</t>
         </is>
       </c>
     </row>
@@ -6998,12 +6998,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>52013</t>
+          <t>50852</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>81615</t>
+          <t>80567</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7013,12 +7013,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7033,12 +7033,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>38540</t>
+          <t>37816</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>64279</t>
+          <t>62024</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7048,12 +7048,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -7068,12 +7068,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>95215</t>
+          <t>96429</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>135604</t>
+          <t>136227</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7083,12 +7083,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,73%</t>
         </is>
       </c>
     </row>
@@ -7111,12 +7111,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>20305</t>
+          <t>20774</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>41354</t>
+          <t>44642</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7126,12 +7126,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7146,12 +7146,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12131</t>
+          <t>12590</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>29906</t>
+          <t>28759</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7161,12 +7161,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7181,12 +7181,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>37080</t>
+          <t>36807</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>64020</t>
+          <t>65657</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7196,12 +7196,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,99%</t>
         </is>
       </c>
     </row>
@@ -7224,12 +7224,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3778</t>
+          <t>3810</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16473</t>
+          <t>16415</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7239,12 +7239,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7259,12 +7259,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6003</t>
+          <t>6787</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>19455</t>
+          <t>20174</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7274,12 +7274,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7294,12 +7294,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>13169</t>
+          <t>12898</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>31394</t>
+          <t>32172</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7309,12 +7309,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,9%</t>
         </is>
       </c>
     </row>
@@ -7454,12 +7454,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>527813</t>
+          <t>527651</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>599838</t>
+          <t>601899</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7469,12 +7469,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>37,58%</t>
+          <t>37,57%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>42,71%</t>
+          <t>42,86%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7489,12 +7489,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>530026</t>
+          <t>528023</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>593148</t>
+          <t>595749</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7504,12 +7504,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>51,34%</t>
+          <t>51,15%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>57,46%</t>
+          <t>57,71%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7524,12 +7524,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1076833</t>
+          <t>1076235</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1181149</t>
+          <t>1180055</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7539,12 +7539,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>44,19%</t>
+          <t>44,17%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>48,47%</t>
+          <t>48,43%</t>
         </is>
       </c>
     </row>
@@ -7567,12 +7567,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>358274</t>
+          <t>358865</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>424951</t>
+          <t>428266</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7582,12 +7582,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>30,49%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7602,12 +7602,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>251137</t>
+          <t>248700</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>305452</t>
+          <t>307421</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7617,12 +7617,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7637,12 +7637,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>627275</t>
+          <t>626324</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>714233</t>
+          <t>717982</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7652,12 +7652,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>29,46%</t>
         </is>
       </c>
     </row>
@@ -7680,12 +7680,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>257171</t>
+          <t>259022</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>318386</t>
+          <t>319377</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7695,12 +7695,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7715,12 +7715,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>114207</t>
+          <t>113954</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>155819</t>
+          <t>155638</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7730,12 +7730,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7750,12 +7750,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>384730</t>
+          <t>383666</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>460270</t>
+          <t>459999</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7765,12 +7765,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>18,88%</t>
         </is>
       </c>
     </row>
@@ -7793,12 +7793,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>134133</t>
+          <t>137587</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>183090</t>
+          <t>184886</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7808,12 +7808,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7828,12 +7828,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>46941</t>
+          <t>45730</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>77315</t>
+          <t>76636</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7863,12 +7863,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>192819</t>
+          <t>192958</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>246530</t>
+          <t>252207</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,35%</t>
         </is>
       </c>
     </row>
@@ -8249,32 +8249,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>17168</t>
+          <t>17812</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10305</t>
+          <t>11045</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26475</t>
+          <t>27611</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>40,47%</t>
+          <t>31,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8284,32 +8284,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>9501</t>
+          <t>10517</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5419</t>
+          <t>6349</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14472</t>
+          <t>16388</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>36,99%</t>
+          <t>35,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8319,32 +8319,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>26668</t>
+          <t>28328</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18976</t>
+          <t>19594</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>36897</t>
+          <t>38420</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,3%</t>
+          <t>28,64%</t>
         </is>
       </c>
     </row>
@@ -8362,32 +8362,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>14713</t>
+          <t>23308</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8955</t>
+          <t>14307</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23308</t>
+          <t>35656</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,63%</t>
+          <t>40,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8397,32 +8397,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>16324</t>
+          <t>20455</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11849</t>
+          <t>15193</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21629</t>
+          <t>26083</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>41,72%</t>
+          <t>44,3%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>32,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>55,28%</t>
+          <t>56,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8432,32 +8432,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>31037</t>
+          <t>43763</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>22473</t>
+          <t>32431</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>40324</t>
+          <t>55831</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>32,63%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>38,57%</t>
+          <t>41,62%</t>
         </is>
       </c>
     </row>
@@ -8475,32 +8475,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>17978</t>
+          <t>23072</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11296</t>
+          <t>14708</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>27457</t>
+          <t>33676</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>41,97%</t>
+          <t>38,29%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8510,32 +8510,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>10594</t>
+          <t>11999</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6625</t>
+          <t>7203</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>16215</t>
+          <t>18245</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>41,45%</t>
+          <t>39,51%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8545,32 +8545,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>28572</t>
+          <t>35072</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>20161</t>
+          <t>25922</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>38189</t>
+          <t>49473</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>36,53%</t>
+          <t>36,88%</t>
         </is>
       </c>
     </row>
@@ -8588,32 +8588,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>15556</t>
+          <t>23761</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9879</t>
+          <t>15423</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24277</t>
+          <t>34155</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,11%</t>
+          <t>38,83%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8623,32 +8623,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2704</t>
+          <t>3206</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>856</t>
+          <t>1230</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6474</t>
+          <t>7132</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8658,32 +8658,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>18260</t>
+          <t>26966</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11988</t>
+          <t>18642</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>27060</t>
+          <t>37414</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>27,89%</t>
         </is>
       </c>
     </row>
@@ -8701,17 +8701,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>65414</t>
+          <t>87953</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>65414</t>
+          <t>87953</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>65414</t>
+          <t>87953</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8736,17 +8736,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>39123</t>
+          <t>46176</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>39123</t>
+          <t>46176</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>39123</t>
+          <t>46176</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8771,17 +8771,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>104537</t>
+          <t>134129</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>104537</t>
+          <t>134129</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>104537</t>
+          <t>134129</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8818,32 +8818,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>403976</t>
+          <t>172177</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>213893</t>
+          <t>148720</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>629958</t>
+          <t>198450</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>50,16%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>78,22%</t>
+          <t>31,96%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8853,32 +8853,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>166198</t>
+          <t>186010</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>126420</t>
+          <t>167940</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>189033</t>
+          <t>206610</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>37,62%</t>
+          <t>40,91%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>36,93%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>42,79%</t>
+          <t>45,44%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8888,32 +8888,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>570175</t>
+          <t>358187</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>389197</t>
+          <t>330422</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>901570</t>
+          <t>391564</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>45,72%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>72,29%</t>
+          <t>36,4%</t>
         </is>
       </c>
     </row>
@@ -8931,32 +8931,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>169910</t>
+          <t>179159</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>76994</t>
+          <t>155105</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>257607</t>
+          <t>202931</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>24,98%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>31,99%</t>
+          <t>32,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8966,32 +8966,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>170134</t>
+          <t>153614</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>141401</t>
+          <t>136751</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>232727</t>
+          <t>171655</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>38,51%</t>
+          <t>33,78%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>32,01%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>52,68%</t>
+          <t>37,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9001,32 +9001,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>340044</t>
+          <t>332773</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>178053</t>
+          <t>302416</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>450538</t>
+          <t>362816</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>30,94%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>36,13%</t>
+          <t>33,73%</t>
         </is>
       </c>
     </row>
@@ -9044,32 +9044,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>153051</t>
+          <t>174895</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>62957</t>
+          <t>151445</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>229872</t>
+          <t>200047</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>32,21%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9079,32 +9079,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>64248</t>
+          <t>71215</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>49414</t>
+          <t>57901</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>80522</t>
+          <t>88145</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9114,32 +9114,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>217299</t>
+          <t>246110</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>107634</t>
+          <t>220694</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>283764</t>
+          <t>276890</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>25,74%</t>
         </is>
       </c>
     </row>
@@ -9157,32 +9157,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>78424</t>
+          <t>94747</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>30334</t>
+          <t>73988</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>121863</t>
+          <t>117390</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9192,32 +9192,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>41175</t>
+          <t>43880</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>28685</t>
+          <t>33500</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>54128</t>
+          <t>56351</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9227,32 +9227,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>119600</t>
+          <t>138627</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>60830</t>
+          <t>116411</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>160596</t>
+          <t>163753</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>15,22%</t>
         </is>
       </c>
     </row>
@@ -9270,17 +9270,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>805362</t>
+          <t>620979</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>805362</t>
+          <t>620979</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>805362</t>
+          <t>620979</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9305,17 +9305,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>441755</t>
+          <t>454719</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>441755</t>
+          <t>454719</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>441755</t>
+          <t>454719</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9340,17 +9340,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1247117</t>
+          <t>1075698</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1247117</t>
+          <t>1075698</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1247117</t>
+          <t>1075698</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9387,32 +9387,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>190549</t>
+          <t>210517</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>174337</t>
+          <t>193897</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>203460</t>
+          <t>223937</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>78,72%</t>
+          <t>78,51%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,02%</t>
+          <t>72,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,05%</t>
+          <t>83,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9422,32 +9422,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>156328</t>
+          <t>169658</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>145078</t>
+          <t>157891</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>165049</t>
+          <t>180457</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>78,53%</t>
+          <t>77,3%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,88%</t>
+          <t>71,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,91%</t>
+          <t>82,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9457,32 +9457,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>346877</t>
+          <t>380176</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>327884</t>
+          <t>358934</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>362285</t>
+          <t>398006</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>78,63%</t>
+          <t>77,97%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,33%</t>
+          <t>73,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,13%</t>
+          <t>81,62%</t>
         </is>
       </c>
     </row>
@@ -9500,32 +9500,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>35725</t>
+          <t>39012</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>24637</t>
+          <t>27746</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>48964</t>
+          <t>52898</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -9535,27 +9535,27 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>29763</t>
+          <t>33245</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>22106</t>
+          <t>24181</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>39772</t>
+          <t>43854</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -9570,32 +9570,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>65488</t>
+          <t>72257</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>52216</t>
+          <t>56640</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>82214</t>
+          <t>87489</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>17,94%</t>
         </is>
       </c>
     </row>
@@ -9613,32 +9613,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>11298</t>
+          <t>12602</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5324</t>
+          <t>6996</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18373</t>
+          <t>20632</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9648,32 +9648,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>6348</t>
+          <t>7831</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3220</t>
+          <t>4027</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11570</t>
+          <t>13892</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9683,32 +9683,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>17647</t>
+          <t>20433</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11581</t>
+          <t>13171</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>26538</t>
+          <t>30566</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,27%</t>
         </is>
       </c>
     </row>
@@ -9726,32 +9726,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4486</t>
+          <t>6002</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>1195</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17649</t>
+          <t>22902</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9761,32 +9761,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>6627</t>
+          <t>8749</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>4327</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13250</t>
+          <t>16619</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9796,32 +9796,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>11114</t>
+          <t>14751</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5110</t>
+          <t>7292</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>22938</t>
+          <t>26675</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,47%</t>
         </is>
       </c>
     </row>
@@ -9839,17 +9839,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>242059</t>
+          <t>268134</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>242059</t>
+          <t>268134</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>242059</t>
+          <t>268134</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9874,17 +9874,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>199066</t>
+          <t>219483</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>199066</t>
+          <t>219483</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>199066</t>
+          <t>219483</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9909,17 +9909,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>441125</t>
+          <t>487617</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>441125</t>
+          <t>487617</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>441125</t>
+          <t>487617</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9956,32 +9956,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>611693</t>
+          <t>400507</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>458111</t>
+          <t>368813</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>831639</t>
+          <t>433011</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>54,97%</t>
+          <t>40,99%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>41,17%</t>
+          <t>37,75%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>74,73%</t>
+          <t>44,32%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9991,32 +9991,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>332027</t>
+          <t>366185</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>271170</t>
+          <t>342639</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>360247</t>
+          <t>391698</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>48,83%</t>
+          <t>50,83%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>39,88%</t>
+          <t>47,56%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>52,98%</t>
+          <t>54,37%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10026,32 +10026,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>943720</t>
+          <t>766691</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>787313</t>
+          <t>720901</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1240708</t>
+          <t>810673</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>52,64%</t>
+          <t>45,17%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>43,92%</t>
+          <t>42,47%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>69,21%</t>
+          <t>47,76%</t>
         </is>
       </c>
     </row>
@@ -10069,32 +10069,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>220349</t>
+          <t>241480</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>124808</t>
+          <t>212513</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>292637</t>
+          <t>276023</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10104,32 +10104,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>216220</t>
+          <t>207314</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>183920</t>
+          <t>186720</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>305646</t>
+          <t>229505</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>31,8%</t>
+          <t>28,78%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>25,92%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>44,95%</t>
+          <t>31,86%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10139,32 +10139,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>436569</t>
+          <t>448794</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>280873</t>
+          <t>415174</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>527908</t>
+          <t>488077</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>24,46%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>28,75%</t>
         </is>
       </c>
     </row>
@@ -10182,32 +10182,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>182327</t>
+          <t>210569</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>92489</t>
+          <t>180468</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>245096</t>
+          <t>240062</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10217,32 +10217,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>81190</t>
+          <t>91045</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>65527</t>
+          <t>76338</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>99650</t>
+          <t>109255</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10252,32 +10252,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>263517</t>
+          <t>301615</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>172609</t>
+          <t>268114</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>322327</t>
+          <t>332151</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>19,57%</t>
         </is>
       </c>
     </row>
@@ -10295,32 +10295,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>98466</t>
+          <t>124510</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>56064</t>
+          <t>98821</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>135200</t>
+          <t>150214</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10330,32 +10330,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>50507</t>
+          <t>55834</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>37367</t>
+          <t>42202</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>63958</t>
+          <t>68914</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10365,32 +10365,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>148973</t>
+          <t>180344</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>96146</t>
+          <t>153105</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>186440</t>
+          <t>209982</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>12,37%</t>
         </is>
       </c>
     </row>
@@ -10408,17 +10408,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1112835</t>
+          <t>977066</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1112835</t>
+          <t>977066</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1112835</t>
+          <t>977066</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10443,17 +10443,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>679944</t>
+          <t>720378</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>679944</t>
+          <t>720378</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>679944</t>
+          <t>720378</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10478,17 +10478,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1792779</t>
+          <t>1697444</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1792779</t>
+          <t>1697444</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1792779</t>
+          <t>1697444</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
